--- a/artfynd/A 18120-2026 artfynd.xlsx
+++ b/artfynd/A 18120-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119302611</v>
+        <v>119302612</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589534</v>
+        <v>589515</v>
       </c>
       <c r="R2" t="n">
-        <v>6766605</v>
+        <v>6766563</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ungt tallbestånd</t>
+          <t>ung sumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119302612</v>
+        <v>119302608</v>
       </c>
       <c r="B3" t="n">
-        <v>58138</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589515</v>
+        <v>589535</v>
       </c>
       <c r="R3" t="n">
-        <v>6766563</v>
+        <v>6766490</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,6 +850,11 @@
           <t>2024-06-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -871,7 +866,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>ung sumpskog</t>
+          <t>äldre tallsumpskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -889,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119302615</v>
+        <v>119302609</v>
       </c>
       <c r="B4" t="n">
-        <v>97824</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589492</v>
+        <v>589508</v>
       </c>
       <c r="R4" t="n">
-        <v>6766805</v>
+        <v>6766538</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -965,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,12 +994,7 @@
         <v>119302610</v>
       </c>
       <c r="B5" t="n">
-        <v>97824</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,6 +1090,312 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119302611</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr om Stortjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>589534</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6766605</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>ungt tallbestånd</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119302614</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr om Stortjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589492</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6766735</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>fuktigt tallungskogsbestånd</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119302615</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr om Stortjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589492</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6766805</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre tallsumpskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
